--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484167_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484167_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5776</v>
+        <v>10.9219</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9099</v>
+        <v>11.1139</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3323</v>
+        <v>-0.192</v>
       </c>
       <c r="G2" t="n">
         <v>10.025</v>
@@ -610,13 +610,13 @@
         <v>1.3887</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1559</v>
+        <v>0.5002</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5669</v>
+        <v>0.7709</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.411</v>
+        <v>-0.2707</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>10.0872</v>
+        <v>10.4213</v>
       </c>
       <c r="E3" t="n">
-        <v>10.2497</v>
+        <v>10.5558</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1625</v>
+        <v>-0.1345</v>
       </c>
       <c r="G3" t="n">
         <v>6.2749</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4155</v>
+        <v>0.7496</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1814</v>
+        <v>0.4875</v>
       </c>
       <c r="U3" t="n">
-        <v>0.234</v>
+        <v>0.2621</v>
       </c>
       <c r="V3" t="n">
         <v>1.8097</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>9.0816</v>
+        <v>8.978199999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>8.574199999999999</v>
+        <v>8.330399999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5075</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>5.8357</v>
@@ -766,13 +766,13 @@
         <v>2.579</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8734</v>
+        <v>1.7699</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2924</v>
+        <v>1.0487</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5809</v>
+        <v>0.7212</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2065</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.3604</v>
+        <v>4.9764</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9923</v>
+        <v>3.7485</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3681</v>
+        <v>1.2278</v>
       </c>
       <c r="G5" t="n">
         <v>2.019</v>
@@ -844,13 +844,13 @@
         <v>1.9838</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3575</v>
+        <v>0.9735</v>
       </c>
       <c r="T5" t="n">
-        <v>1.06</v>
+        <v>0.8163</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2975</v>
+        <v>0.1572</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>P. RIOS CADENAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.7931</v>
+        <v>4.7669</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2261</v>
+        <v>3.2008</v>
       </c>
       <c r="F6" t="n">
-        <v>1.567</v>
+        <v>1.5661</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0107</v>
+        <v>3.5726</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2882</v>
+        <v>-0.0756</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2775</v>
+        <v>3.6482</v>
       </c>
       <c r="J6" t="n">
-        <v>1.996</v>
+        <v>4.617</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1505</v>
+        <v>0.7163</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1545</v>
+        <v>3.9008</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9853</v>
+        <v>-1.0444</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8623</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.123</v>
+        <v>-0.2526</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1903</v>
+        <v>-2.3806</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-4.9596</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1822</v>
+        <v>2.579</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5921</v>
+        <v>1.4992</v>
       </c>
       <c r="T6" t="n">
-        <v>2.222</v>
+        <v>1.2017</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3701</v>
+        <v>0.2975</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.3417</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. RIOS CADENAS</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.5567</v>
+        <v>3.9653</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9344</v>
+        <v>2.3702</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6222</v>
+        <v>1.5951</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5726</v>
+        <v>1.0107</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0756</v>
+        <v>2.2882</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6482</v>
+        <v>-1.2775</v>
       </c>
       <c r="J7" t="n">
-        <v>4.617</v>
+        <v>1.996</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7163</v>
+        <v>3.1505</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9008</v>
+        <v>-1.1545</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0444</v>
+        <v>-0.9853</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.8623</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2526</v>
+        <v>-0.123</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3806</v>
+        <v>1.1903</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.9596</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>2.579</v>
+        <v>2.1822</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2889</v>
+        <v>1.7642</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9353</v>
+        <v>1.3661</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3536</v>
+        <v>0.3981</v>
       </c>
       <c r="V7" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3417</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.6007</v>
+        <v>3.4105</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8483</v>
+        <v>3.9106</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2476</v>
+        <v>-0.5001</v>
       </c>
       <c r="G8" t="n">
         <v>1.9439</v>
@@ -1078,13 +1078,13 @@
         <v>0.5952</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0616</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1191</v>
+        <v>0.1814</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9425</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. NDOUR</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4225</v>
+        <v>1.3426</v>
       </c>
       <c r="E9" t="n">
-        <v>1.038</v>
+        <v>-0.2584</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6155</v>
+        <v>1.601</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5976</v>
+        <v>-0.9384</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6804</v>
+        <v>-1.0032</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9172</v>
+        <v>0.0648</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0107</v>
+        <v>0.1732</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2918</v>
+        <v>-0.1507</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2811</v>
+        <v>0.3238</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5869</v>
+        <v>-1.1116</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3886</v>
+        <v>-0.8525</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1983</v>
+        <v>-0.2591</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7935</v>
+        <v>3.5709</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2266</v>
+        <v>1.0826</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0487</v>
+        <v>1.3378</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1779</v>
+        <v>-0.2551</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>S. NDOUR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0144</v>
+        <v>-0.0417</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2787</v>
+        <v>0.6299</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2643</v>
+        <v>-0.6716</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9384</v>
+        <v>-1.5976</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0032</v>
+        <v>-0.6804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0648</v>
+        <v>-0.9172</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1732</v>
+        <v>-0.0107</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1507</v>
+        <v>-0.2918</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3238</v>
+        <v>0.2811</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1116</v>
+        <v>-1.5869</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8525</v>
+        <v>-0.3886</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2591</v>
+        <v>-1.1983</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.5709</v>
+        <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2743</v>
+        <v>0.7624</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3175</v>
+        <v>0.6405</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5918</v>
+        <v>0.1218</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8575</v>
+        <v>-0.4035</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0364</v>
+        <v>-2.5262</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1789</v>
+        <v>2.1228</v>
       </c>
       <c r="G11" t="n">
         <v>-3.8181</v>
@@ -1312,13 +1312,13 @@
         <v>2.1822</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8298</v>
+        <v>1.2839</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2438</v>
+        <v>0.7539</v>
       </c>
       <c r="U11" t="n">
-        <v>0.586</v>
+        <v>0.5299</v>
       </c>
       <c r="V11" t="n">
         <v>0.9405</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8752</v>
+        <v>-3.2935</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9244</v>
+        <v>-1.2305</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9508</v>
+        <v>-2.063</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6401</v>
@@ -1390,13 +1390,13 @@
         <v>1.3887</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1778</v>
+        <v>0.7595</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9977</v>
+        <v>0.6916</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1802</v>
+        <v>0.0679</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8097</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>44.73269999999999</v>
+        <v>45.0444</v>
       </c>
       <c r="E13" t="n">
-        <v>39.53340000000001</v>
+        <v>39.84499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1993</v>
+        <v>5.199300000000001</v>
       </c>
       <c r="G13" t="n">
         <v>21.6876</v>
@@ -1453,13 +1453,13 @@
         <v>-15.1403</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.238</v>
+        <v>-7.238000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.9024</v>
+        <v>-7.902399999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>8.927400000000002</v>
+        <v>8.9274</v>
       </c>
       <c r="Q13" t="n">
         <v>-11.903</v>
@@ -1468,10 +1468,10 @@
         <v>20.8303</v>
       </c>
       <c r="S13" t="n">
-        <v>11.7048</v>
+        <v>12.0165</v>
       </c>
       <c r="T13" t="n">
-        <v>8.9848</v>
+        <v>9.2964</v>
       </c>
       <c r="U13" t="n">
         <v>2.7199</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0542</v>
+        <v>2.3688</v>
       </c>
       <c r="E14" t="n">
-        <v>8.974600000000001</v>
+        <v>8.8726</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.9204</v>
+        <v>-6.5039</v>
       </c>
       <c r="G14" t="n">
         <v>2.738</v>
@@ -1546,13 +1546,13 @@
         <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9498</v>
+        <v>-1.6352</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5667</v>
+        <v>-0.6687</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3831</v>
+        <v>-0.9665</v>
       </c>
       <c r="V14" t="n">
         <v>0.8692</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.6544</v>
+        <v>-3.18</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.4882</v>
+        <v>-2.1821</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1662</v>
+        <v>-0.9979</v>
       </c>
       <c r="G15" t="n">
         <v>0.8925999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7696</v>
+        <v>-1.2952</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2494</v>
+        <v>0.0567</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.5202</v>
+        <v>-1.3519</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. SERRA DE MUNTER</t>
+          <t>M. MANYOSES ROCA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.8457</v>
+        <v>-3.4792</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2555</v>
+        <v>0.5349</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.5902</v>
+        <v>-4.014</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2992</v>
+        <v>-2.3403</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5794</v>
+        <v>-1.4516</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8785</v>
+        <v>-0.8887</v>
       </c>
       <c r="J16" t="n">
-        <v>0.555</v>
+        <v>0.2466</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9154</v>
+        <v>0.0859</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3604</v>
+        <v>0.1606</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8541</v>
+        <v>-2.5869</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.336</v>
+        <v>-1.5376</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5182</v>
+        <v>-1.0493</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6773</v>
+        <v>-0.3373</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1814</v>
+        <v>0.0737</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8588</v>
+        <v>-0.411</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4724</v>
+        <v>-0.6032</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4724</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MANYOSES ROCA</t>
+          <t>F. SERRA DE MUNTER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.1815</v>
+        <v>-4.0115</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0247</v>
+        <v>-0.5616</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.2062</v>
+        <v>-3.4499</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3403</v>
+        <v>-1.2992</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4516</v>
+        <v>0.5794</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8887</v>
+        <v>-1.8785</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2466</v>
+        <v>0.555</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0859</v>
+        <v>1.9154</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1606</v>
+        <v>-1.3604</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5869</v>
+        <v>-1.8541</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5376</v>
+        <v>-1.336</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0493</v>
+        <v>-0.5182</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0396</v>
+        <v>-0.8431</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4364</v>
+        <v>-0.1247</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6031</v>
+        <v>-0.7185</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6032</v>
+        <v>-1.4724</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8097</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.842</v>
+        <v>-4.1116</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.669</v>
+        <v>-1.1589</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.1729</v>
+        <v>-2.9527</v>
       </c>
       <c r="G18" t="n">
         <v>-3.0389</v>
@@ -1858,13 +1858,13 @@
         <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0095</v>
+        <v>-0.2792</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2494</v>
+        <v>0.2608</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7601</v>
+        <v>-0.5399</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. MALARY</t>
+          <t>D. COFFIE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.4913</v>
+        <v>-5.7459</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8603</v>
+        <v>-2.8555</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.3516</v>
+        <v>-2.8904</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9727</v>
+        <v>-5.2684</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1991</v>
+        <v>-2.3988</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7736</v>
+        <v>-2.8696</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0027</v>
+        <v>-2.4192</v>
       </c>
       <c r="K19" t="n">
-        <v>0.868</v>
+        <v>-1.9398</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1347</v>
+        <v>-0.4794</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.9754</v>
+        <v>-2.8492</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.0671</v>
+        <v>-0.459</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.9083</v>
+        <v>-2.3902</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3968</v>
+        <v>0.3968</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2526</v>
+        <v>-0.8743</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2382</v>
+        <v>-0.4364</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4908</v>
+        <v>-0.4379</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. COFFIE</t>
+          <t>L. MALARY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.524</v>
+        <v>-6.1035</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5495</v>
+        <v>0.2481</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9746</v>
+        <v>-6.3516</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.2684</v>
+        <v>-2.9727</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3988</v>
+        <v>-1.1991</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.8696</v>
+        <v>-1.7736</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4192</v>
+        <v>2.0027</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9398</v>
+        <v>0.868</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4794</v>
+        <v>1.1347</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8492</v>
+        <v>-4.9754</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.459</v>
+        <v>-2.0671</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.3902</v>
+        <v>-2.9083</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3968</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6524</v>
+        <v>-1.8648</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1303</v>
+        <v>-0.374</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5221</v>
+        <v>-1.4908</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. NDIAYE</t>
+          <t>D. MARTIN VELA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.7949</v>
+        <v>-6.3383</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3647</v>
+        <v>-3.4379</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.4302</v>
+        <v>-2.9004</v>
       </c>
       <c r="G21" t="n">
-        <v>-6.2665</v>
+        <v>-3.6109</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3878</v>
+        <v>-1.6535</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.8787</v>
+        <v>-1.9575</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3469</v>
+        <v>-0.2978</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5879</v>
+        <v>-0.4584</v>
       </c>
       <c r="L21" t="n">
-        <v>0.241</v>
+        <v>0.1606</v>
       </c>
       <c r="M21" t="n">
-        <v>-5.9196</v>
+        <v>-3.3132</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7999</v>
+        <v>-1.195</v>
       </c>
       <c r="O21" t="n">
-        <v>-4.1197</v>
+        <v>-2.1181</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7935</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>0.662</v>
+        <v>-1.1917</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3629</v>
+        <v>-0.4817</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2991</v>
+        <v>-0.71</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6032</v>
+        <v>-0.9405</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6032</v>
+        <v>-0.6745</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.6907</v>
+        <v>-6.609</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0902</v>
+        <v>-2.7841</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6005</v>
+        <v>-3.8249</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5214</v>
@@ -2170,13 +2170,13 @@
         <v>2.1822</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3999</v>
+        <v>-2.3183</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1846</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2154</v>
+        <v>-1.4398</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. MARTIN VELA</t>
+          <t>L. NDIAYE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.7626</v>
+        <v>-6.8423</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6419</v>
+        <v>-1.8748</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1207</v>
+        <v>-4.9675</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6109</v>
+        <v>-6.2665</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6535</v>
+        <v>-2.3878</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9575</v>
+        <v>-3.8787</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2978</v>
+        <v>-0.3469</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4584</v>
+        <v>-0.5879</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1606</v>
+        <v>0.241</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.3132</v>
+        <v>-5.9196</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.195</v>
+        <v>-1.7999</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1181</v>
+        <v>-4.1197</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5952</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3887</v>
+        <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.616</v>
+        <v>-0.3855</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6858</v>
+        <v>-0.1473</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9302</v>
+        <v>-0.2382</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9405</v>
+        <v>0.6032</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6745</v>
+        <v>0.6032</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-44.7329</v>
+        <v>-44.0525</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.1994</v>
+        <v>-5.1993</v>
       </c>
       <c r="F24" t="n">
-        <v>-39.5335</v>
+        <v>-38.8532</v>
       </c>
       <c r="G24" t="n">
         <v>-21.6877</v>
       </c>
       <c r="H24" t="n">
-        <v>-7.7612</v>
+        <v>-7.761199999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-13.9266</v>
@@ -2302,13 +2302,13 @@
         <v>15.1402</v>
       </c>
       <c r="K24" t="n">
-        <v>7.2379</v>
+        <v>7.237899999999999</v>
       </c>
       <c r="L24" t="n">
         <v>7.9021</v>
       </c>
       <c r="M24" t="n">
-        <v>-36.82790000000001</v>
+        <v>-36.8279</v>
       </c>
       <c r="N24" t="n">
         <v>-14.9991</v>
@@ -2326,19 +2326,19 @@
         <v>11.9031</v>
       </c>
       <c r="S24" t="n">
-        <v>-11.7047</v>
+        <v>-11.0246</v>
       </c>
       <c r="T24" t="n">
         <v>-2.7201</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.984699999999998</v>
+        <v>-8.304500000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4129</v>
       </c>
       <c r="W24" t="n">
-        <v>3.210799999999999</v>
+        <v>3.2108</v>
       </c>
       <c r="X24" t="n">
         <v>-5.623699999999999</v>
